--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DAFAE4-3F96-4FBC-92F2-AEDCEC518E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93349559-E1A5-4041-9329-D15991F860E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>Familia</t>
   </si>
   <si>
-    <t>Género</t>
-  </si>
-  <si>
     <t>Latitud</t>
   </si>
   <si>
@@ -578,6 +575,9 @@
   </si>
   <si>
     <t>Especie</t>
+  </si>
+  <si>
+    <t>Genero</t>
   </si>
 </sst>
 </file>
@@ -922,6 +922,12 @@
   <cols>
     <col min="1" max="1" width="43.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -943,45 +949,45 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
       </c>
       <c r="H2">
         <v>-12.057342</v>
@@ -990,65 +996,65 @@
         <v>-77.085965999999999</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
       </c>
       <c r="I3">
         <v>-77.081864663826892</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
       </c>
       <c r="H4">
         <v>-12.060062</v>
@@ -1057,33 +1063,33 @@
         <v>-77.083754999999996</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
       </c>
       <c r="H5">
         <v>-12.057245</v>
@@ -1092,33 +1098,33 @@
         <v>-77.086871000000002</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
       </c>
       <c r="H6">
         <v>-12.054695000000001</v>
@@ -1127,33 +1133,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
       </c>
       <c r="H7">
         <v>-12.053594</v>
@@ -1162,33 +1168,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>41</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
       </c>
       <c r="H8">
         <v>-12.053594</v>
@@ -1197,33 +1203,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>47</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
       </c>
       <c r="H9">
         <v>-12.053938</v>
@@ -1232,33 +1238,33 @@
         <v>-77.086535999999995</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>50</v>
-      </c>
-      <c r="G10" t="s">
-        <v>51</v>
       </c>
       <c r="H10">
         <v>-12.053748000000001</v>
@@ -1267,33 +1273,33 @@
         <v>-77.085588000000001</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
         <v>52</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>53</v>
-      </c>
-      <c r="G11" t="s">
-        <v>54</v>
       </c>
       <c r="H11">
         <v>-12.060318000000001</v>
@@ -1302,33 +1308,33 @@
         <v>-77.084213000000005</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>57</v>
-      </c>
-      <c r="G12" t="s">
-        <v>58</v>
       </c>
       <c r="H12">
         <v>-12.060318000000001</v>
@@ -1337,33 +1343,33 @@
         <v>-77.084213000000005</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>60</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>61</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>62</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
       </c>
       <c r="H13">
         <v>-12.057501</v>
@@ -1372,33 +1378,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>35</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>36</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>38</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
       </c>
       <c r="H14">
         <v>-12.057501</v>
@@ -1407,33 +1413,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" t="s">
         <v>66</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>67</v>
-      </c>
-      <c r="G15" t="s">
-        <v>68</v>
       </c>
       <c r="H15">
         <v>-12.057501</v>
@@ -1442,33 +1448,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
       <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
       <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
         <v>50</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
       </c>
       <c r="H16">
         <v>-12.059274</v>
@@ -1477,65 +1483,65 @@
         <v>-77.080799999999996</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>71</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>73</v>
       </c>
       <c r="I17">
         <v>-77.081646996680064</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>76</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>77</v>
-      </c>
-      <c r="G18" t="s">
-        <v>78</v>
       </c>
       <c r="H18">
         <v>-12.057501</v>
@@ -1544,33 +1550,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>79</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
       </c>
       <c r="H19">
         <v>-12.059339</v>
@@ -1579,33 +1585,33 @@
         <v>-77.087202000000005</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>81</v>
       </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>82</v>
-      </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H20">
         <v>-12057853</v>
@@ -1614,33 +1620,33 @@
         <v>-77079891</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
       <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
         <v>41</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>43</v>
       </c>
       <c r="H21">
         <v>-12057853</v>
@@ -1649,33 +1655,33 @@
         <v>-77079891</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
         <v>34</v>
       </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
       <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
         <v>60</v>
       </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
       <c r="F22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s">
         <v>83</v>
-      </c>
-      <c r="G22" t="s">
-        <v>84</v>
       </c>
       <c r="H22">
         <v>-12057853</v>
@@ -1684,33 +1690,33 @@
         <v>-77079891</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
         <v>34</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>35</v>
       </c>
-      <c r="D23" t="s">
-        <v>36</v>
-      </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" t="s">
         <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
       </c>
       <c r="H23">
         <v>-12057853</v>
@@ -1719,33 +1725,33 @@
         <v>-77079891</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
         <v>34</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>35</v>
       </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" t="s">
         <v>87</v>
-      </c>
-      <c r="G24" t="s">
-        <v>88</v>
       </c>
       <c r="H24">
         <v>-12058354</v>
@@ -1754,33 +1760,33 @@
         <v>-77079760</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
         <v>34</v>
       </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>45</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>46</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>47</v>
-      </c>
-      <c r="G25" t="s">
-        <v>48</v>
       </c>
       <c r="H25">
         <v>-12.054439</v>
@@ -1789,33 +1795,33 @@
         <v>-77.085120000000003</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
         <v>34</v>
       </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>45</v>
       </c>
-      <c r="E26" t="s">
-        <v>46</v>
-      </c>
       <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
         <v>50</v>
-      </c>
-      <c r="G26" t="s">
-        <v>51</v>
       </c>
       <c r="H26">
         <v>-12.054391000000001</v>
@@ -1824,33 +1830,33 @@
         <v>-77.084608000000003</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
         <v>34</v>
       </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>45</v>
       </c>
-      <c r="E27" t="s">
-        <v>46</v>
-      </c>
       <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
         <v>50</v>
-      </c>
-      <c r="G27" t="s">
-        <v>51</v>
       </c>
       <c r="H27">
         <v>-12.054632</v>
@@ -1859,33 +1865,33 @@
         <v>-77.083718000000005</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
         <v>34</v>
       </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>45</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>46</v>
       </c>
-      <c r="F28" t="s">
-        <v>47</v>
-      </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28">
         <v>-12.054871</v>
@@ -1894,33 +1900,33 @@
         <v>-77.084220999999999</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
         <v>34</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>35</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>36</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>37</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>38</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
       </c>
       <c r="H29">
         <v>-12.054997</v>
@@ -1929,33 +1935,33 @@
         <v>-77.084431300000006</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>91</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>92</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>93</v>
-      </c>
-      <c r="G30" t="s">
-        <v>94</v>
       </c>
       <c r="H30">
         <v>-12.0567391</v>
@@ -1964,33 +1970,33 @@
         <v>-77.085449600000004</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
         <v>95</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>96</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>97</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>98</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>99</v>
-      </c>
-      <c r="G31" t="s">
-        <v>100</v>
       </c>
       <c r="H31">
         <v>-12.057642400000001</v>
@@ -1999,33 +2005,33 @@
         <v>-77.085686300000006</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
         <v>101</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>102</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>103</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>104</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>105</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>106</v>
-      </c>
-      <c r="G32" t="s">
-        <v>107</v>
       </c>
       <c r="H32">
         <v>-12.056699999999999</v>
@@ -2034,33 +2040,33 @@
         <v>-77.084999999999994</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>103</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>104</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>105</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>106</v>
-      </c>
-      <c r="G33" t="s">
-        <v>107</v>
       </c>
       <c r="H33">
         <v>-12.059274</v>
@@ -2069,33 +2075,33 @@
         <v>-77.080799999999996</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" t="s">
         <v>102</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>103</v>
       </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
       <c r="E34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" t="s">
         <v>109</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>110</v>
-      </c>
-      <c r="G34" t="s">
-        <v>111</v>
       </c>
       <c r="H34">
         <v>-12.054695000000001</v>
@@ -2104,33 +2110,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
         <v>102</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>103</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>104</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>105</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>106</v>
-      </c>
-      <c r="G35" t="s">
-        <v>107</v>
       </c>
       <c r="H35">
         <v>-12.054695000000001</v>
@@ -2139,33 +2145,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
         <v>102</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>103</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>104</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>105</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>106</v>
-      </c>
-      <c r="G36" t="s">
-        <v>107</v>
       </c>
       <c r="H36">
         <v>-12058012</v>
@@ -2174,33 +2180,33 @@
         <v>-77079983</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" t="s">
         <v>113</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>114</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>115</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>116</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s">
         <v>117</v>
-      </c>
-      <c r="F37" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" t="s">
-        <v>118</v>
       </c>
       <c r="H37">
         <v>-12.059456000000001</v>
@@ -2209,33 +2215,33 @@
         <v>-77.090440999999998</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" t="s">
         <v>119</v>
       </c>
-      <c r="B38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>120</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>121</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>122</v>
-      </c>
-      <c r="G38" t="s">
-        <v>123</v>
       </c>
       <c r="H38">
         <v>-12.059456000000001</v>
@@ -2244,33 +2250,33 @@
         <v>-77.090440999999998</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" t="s">
         <v>124</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>121</v>
-      </c>
-      <c r="F39" t="s">
-        <v>122</v>
-      </c>
-      <c r="G39" t="s">
-        <v>125</v>
       </c>
       <c r="H39">
         <v>-12.057059000000001</v>
@@ -2279,33 +2285,33 @@
         <v>-77.087091000000001</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" t="s">
         <v>126</v>
       </c>
-      <c r="B40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>127</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>128</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>129</v>
-      </c>
-      <c r="G40" t="s">
-        <v>130</v>
       </c>
       <c r="H40">
         <v>-12.054278999999999</v>
@@ -2314,33 +2320,33 @@
         <v>-77.085412000000005</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s">
         <v>131</v>
       </c>
-      <c r="B41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>132</v>
-      </c>
-      <c r="G41" t="s">
-        <v>133</v>
       </c>
       <c r="H41">
         <v>-12.056659</v>
@@ -2349,33 +2355,33 @@
         <v>-77.086890999999994</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
         <v>134</v>
       </c>
-      <c r="B42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>135</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" t="s">
         <v>136</v>
-      </c>
-      <c r="F42" t="s">
-        <v>135</v>
-      </c>
-      <c r="G42" t="s">
-        <v>137</v>
       </c>
       <c r="H42">
         <v>-12.053594</v>
@@ -2384,33 +2390,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" t="s">
         <v>138</v>
       </c>
-      <c r="B43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>139</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>140</v>
-      </c>
-      <c r="G43" t="s">
-        <v>141</v>
       </c>
       <c r="H43">
         <v>-12.055809999999999</v>
@@ -2419,33 +2425,33 @@
         <v>-77.022840000000002</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" t="s">
         <v>142</v>
       </c>
-      <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>143</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>144</v>
-      </c>
-      <c r="G44" t="s">
-        <v>145</v>
       </c>
       <c r="H44">
         <v>-12.056839999999999</v>
@@ -2454,33 +2460,33 @@
         <v>-77.086288999999994</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" t="s">
         <v>146</v>
       </c>
-      <c r="B45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>147</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>148</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>149</v>
-      </c>
-      <c r="G45" t="s">
-        <v>150</v>
       </c>
       <c r="H45">
         <v>-12.05791188888888</v>
@@ -2489,65 +2495,65 @@
         <v>-77.085793888888887</v>
       </c>
       <c r="J45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
         <v>151</v>
       </c>
-      <c r="B46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>152</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>153</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>154</v>
-      </c>
-      <c r="G46" t="s">
-        <v>155</v>
       </c>
       <c r="I46">
         <v>-77.081646996680064</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" t="s">
+        <v>152</v>
+      </c>
+      <c r="F47" t="s">
         <v>156</v>
       </c>
-      <c r="B47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
-        <v>152</v>
-      </c>
-      <c r="E47" t="s">
-        <v>153</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>157</v>
-      </c>
-      <c r="G47" t="s">
-        <v>158</v>
       </c>
       <c r="H47">
         <v>-12.059383211096049</v>
@@ -2556,33 +2562,33 @@
         <v>-77.080684001513475</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
         <v>114</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>115</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>116</v>
       </c>
-      <c r="E48" t="s">
-        <v>117</v>
-      </c>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H48">
         <v>-12058578</v>
@@ -2591,33 +2597,33 @@
         <v>-77079825</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" t="s">
         <v>114</v>
       </c>
-      <c r="C49" t="s">
-        <v>115</v>
-      </c>
       <c r="D49" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" t="s">
         <v>127</v>
       </c>
-      <c r="E49" t="s">
-        <v>128</v>
-      </c>
       <c r="F49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H49">
         <v>-12058521</v>
@@ -2626,33 +2632,33 @@
         <v>-77079742</v>
       </c>
       <c r="J49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" t="s">
         <v>114</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>115</v>
       </c>
-      <c r="D50" t="s">
-        <v>116</v>
-      </c>
       <c r="E50" t="s">
+        <v>142</v>
+      </c>
+      <c r="F50" t="s">
         <v>143</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>144</v>
-      </c>
-      <c r="G50" t="s">
-        <v>145</v>
       </c>
       <c r="H50">
         <v>-12058225</v>
@@ -2661,33 +2667,33 @@
         <v>-77079769</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
         <v>114</v>
       </c>
-      <c r="C51" t="s">
-        <v>115</v>
-      </c>
       <c r="D51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" t="s">
         <v>127</v>
       </c>
-      <c r="E51" t="s">
-        <v>128</v>
-      </c>
       <c r="F51" t="s">
+        <v>131</v>
+      </c>
+      <c r="G51" t="s">
         <v>132</v>
-      </c>
-      <c r="G51" t="s">
-        <v>133</v>
       </c>
       <c r="H51">
         <v>-12.054695000000001</v>
@@ -2696,33 +2702,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" t="s">
         <v>114</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>115</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>116</v>
       </c>
-      <c r="E52" t="s">
-        <v>117</v>
-      </c>
       <c r="F52" t="s">
+        <v>161</v>
+      </c>
+      <c r="G52" t="s">
         <v>162</v>
-      </c>
-      <c r="G52" t="s">
-        <v>163</v>
       </c>
       <c r="H52">
         <v>-12.054695000000001</v>
@@ -2731,33 +2737,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s">
         <v>114</v>
       </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
       <c r="D53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" t="s">
         <v>164</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>165</v>
-      </c>
-      <c r="G53" t="s">
-        <v>166</v>
       </c>
       <c r="H53">
         <v>-12.054695000000001</v>
@@ -2766,33 +2772,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>115</v>
       </c>
-      <c r="D54" t="s">
-        <v>116</v>
-      </c>
       <c r="E54" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" t="s">
         <v>143</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>144</v>
-      </c>
-      <c r="G54" t="s">
-        <v>145</v>
       </c>
       <c r="H54">
         <v>-12.054695000000001</v>
@@ -2801,33 +2807,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" t="s">
         <v>114</v>
       </c>
-      <c r="C55" t="s">
-        <v>115</v>
-      </c>
       <c r="D55" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" t="s">
         <v>167</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
+        <v>114</v>
+      </c>
+      <c r="G55" t="s">
         <v>168</v>
-      </c>
-      <c r="F55" t="s">
-        <v>115</v>
-      </c>
-      <c r="G55" t="s">
-        <v>169</v>
       </c>
       <c r="H55">
         <v>-12.0592408</v>
@@ -2836,33 +2842,33 @@
         <v>-77.083485899999999</v>
       </c>
       <c r="J55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" t="s">
         <v>114</v>
       </c>
-      <c r="C56" t="s">
-        <v>115</v>
-      </c>
       <c r="D56" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" t="s">
         <v>170</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>171</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>172</v>
-      </c>
-      <c r="G56" t="s">
-        <v>173</v>
       </c>
       <c r="H56">
         <v>-12.058871999999999</v>
@@ -2871,33 +2877,33 @@
         <v>-77.084579500000004</v>
       </c>
       <c r="J56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" t="s">
         <v>174</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>175</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>176</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>177</v>
-      </c>
-      <c r="G57" t="s">
-        <v>178</v>
       </c>
       <c r="H57">
         <v>-12.058732900000001</v>
@@ -2906,33 +2912,33 @@
         <v>-77.084835699999999</v>
       </c>
       <c r="J57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" t="s">
         <v>179</v>
       </c>
-      <c r="B58" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>180</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>181</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>182</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>183</v>
-      </c>
-      <c r="G58" t="s">
-        <v>184</v>
       </c>
       <c r="H58">
         <v>-12.059339</v>
@@ -2941,10 +2947,10 @@
         <v>-77.087202000000005</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93349559-E1A5-4041-9329-D15991F860E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70538222-9821-4585-B104-E375EBF398AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="187">
   <si>
     <t>Archivo Origen</t>
   </si>
@@ -37,18 +37,24 @@
     <t>Familia</t>
   </si>
   <si>
+    <t>Genero</t>
+  </si>
+  <si>
+    <t>Especie</t>
+  </si>
+  <si>
     <t>Latitud</t>
   </si>
   <si>
     <t>Longitud</t>
   </si>
   <si>
-    <t>Estado de Conservacion</t>
-  </si>
-  <si>
     <t>Origen</t>
   </si>
   <si>
+    <t>Estado</t>
+  </si>
+  <si>
     <t>FAU-04.pdf</t>
   </si>
   <si>
@@ -70,12 +76,12 @@
     <t>Gasteracantha sp.</t>
   </si>
   <si>
+    <t>Nativa</t>
+  </si>
+  <si>
     <t>No Evaluado (NE)</t>
   </si>
   <si>
-    <t>Registrada en GBIF (ACCEPTED)</t>
-  </si>
-  <si>
     <t>FAU-20260417_1.pdf</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>Tityus trivittatus</t>
   </si>
   <si>
+    <t>Exótica</t>
+  </si>
+  <si>
     <t>Fichas-registro-fauna-2026-05-08_UNMSM.pdf</t>
   </si>
   <si>
@@ -139,6 +148,9 @@
     <t>Sicalis flaveola</t>
   </si>
   <si>
+    <t>Preocupación Menor (LC)</t>
+  </si>
+  <si>
     <t>FAU-06.pdf</t>
   </si>
   <si>
@@ -211,9 +223,6 @@
     <t>Amazilia amazilia</t>
   </si>
   <si>
-    <t>Registrada en GBIF (SYNONYM)</t>
-  </si>
-  <si>
     <t>FAU-19.pdf</t>
   </si>
   <si>
@@ -502,9 +511,6 @@
     <t>Coccinellini</t>
   </si>
   <si>
-    <t>Desconocido</t>
-  </si>
-  <si>
     <t>Monomorium</t>
   </si>
   <si>
@@ -574,10 +580,7 @@
     <t>Phyllodactylus sentosus</t>
   </si>
   <si>
-    <t>Especie</t>
-  </si>
-  <si>
-    <t>Genero</t>
+    <t>En Peligro Crítico (CR)</t>
   </si>
 </sst>
 </file>
@@ -928,8 +931,8 @@
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -949,45 +952,45 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>184</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>-12.057342</v>
@@ -996,65 +999,65 @@
         <v>-77.085965999999999</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3">
         <v>-77.081864663826892</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>-12.060062</v>
@@ -1063,33 +1066,33 @@
         <v>-77.083754999999996</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5">
         <v>-12.057245</v>
@@ -1098,33 +1101,33 @@
         <v>-77.086871000000002</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>-12.054695000000001</v>
@@ -1133,33 +1136,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>-12.053594</v>
@@ -1168,33 +1171,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>-12.053594</v>
@@ -1203,33 +1206,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>-12.053938</v>
@@ -1238,33 +1241,33 @@
         <v>-77.086535999999995</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H10">
         <v>-12.053748000000001</v>
@@ -1273,33 +1276,33 @@
         <v>-77.085588000000001</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H11">
         <v>-12.060318000000001</v>
@@ -1308,33 +1311,33 @@
         <v>-77.084213000000005</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H12">
         <v>-12.060318000000001</v>
@@ -1343,33 +1346,33 @@
         <v>-77.084213000000005</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H13">
         <v>-12.057501</v>
@@ -1378,33 +1381,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H14">
         <v>-12.057501</v>
@@ -1413,33 +1416,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H15">
         <v>-12.057501</v>
@@ -1448,33 +1451,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H16">
         <v>-12.059274</v>
@@ -1483,65 +1486,65 @@
         <v>-77.080799999999996</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I17">
         <v>-77.081646996680064</v>
       </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H18">
         <v>-12.057501</v>
@@ -1550,33 +1553,33 @@
         <v>-77.086038000000002</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H19">
         <v>-12.059339</v>
@@ -1585,33 +1588,33 @@
         <v>-77.087202000000005</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H20">
         <v>-12057853</v>
@@ -1620,33 +1623,33 @@
         <v>-77079891</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H21">
         <v>-12057853</v>
@@ -1655,33 +1658,33 @@
         <v>-77079891</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H22">
         <v>-12057853</v>
@@ -1690,33 +1693,33 @@
         <v>-77079891</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H23">
         <v>-12057853</v>
@@ -1725,33 +1728,33 @@
         <v>-77079891</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H24">
         <v>-12058354</v>
@@ -1760,33 +1763,33 @@
         <v>-77079760</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H25">
         <v>-12.054439</v>
@@ -1795,33 +1798,33 @@
         <v>-77.085120000000003</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H26">
         <v>-12.054391000000001</v>
@@ -1830,33 +1833,33 @@
         <v>-77.084608000000003</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H27">
         <v>-12.054632</v>
@@ -1865,33 +1868,33 @@
         <v>-77.083718000000005</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H28">
         <v>-12.054871</v>
@@ -1900,33 +1903,33 @@
         <v>-77.084220999999999</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K28" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G29" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H29">
         <v>-12.054997</v>
@@ -1935,33 +1938,33 @@
         <v>-77.084431300000006</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H30">
         <v>-12.0567391</v>
@@ -1970,33 +1973,33 @@
         <v>-77.085449600000004</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H31">
         <v>-12.057642400000001</v>
@@ -2005,33 +2008,33 @@
         <v>-77.085686300000006</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H32">
         <v>-12.056699999999999</v>
@@ -2040,33 +2043,33 @@
         <v>-77.084999999999994</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
         <v>107</v>
       </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" t="s">
-        <v>104</v>
-      </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H33">
         <v>-12.059274</v>
@@ -2075,33 +2078,33 @@
         <v>-77.080799999999996</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H34">
         <v>-12.054695000000001</v>
@@ -2110,33 +2113,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H35">
         <v>-12.054695000000001</v>
@@ -2145,33 +2148,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H36">
         <v>-12058012</v>
@@ -2180,33 +2183,33 @@
         <v>-77079983</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H37">
         <v>-12.059456000000001</v>
@@ -2215,33 +2218,33 @@
         <v>-77.090440999999998</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H38">
         <v>-12.059456000000001</v>
@@ -2250,33 +2253,33 @@
         <v>-77.090440999999998</v>
       </c>
       <c r="J38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s">
         <v>123</v>
       </c>
-      <c r="B39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" t="s">
-        <v>120</v>
-      </c>
       <c r="F39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H39">
         <v>-12.057059000000001</v>
@@ -2285,33 +2288,33 @@
         <v>-77.087091000000001</v>
       </c>
       <c r="J39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G40" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H40">
         <v>-12.054278999999999</v>
@@ -2320,33 +2323,33 @@
         <v>-77.085412000000005</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s">
         <v>130</v>
       </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>127</v>
-      </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H41">
         <v>-12.056659</v>
@@ -2355,33 +2358,33 @@
         <v>-77.086890999999994</v>
       </c>
       <c r="J41" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H42">
         <v>-12.053594</v>
@@ -2390,33 +2393,33 @@
         <v>-77.085751000000002</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H43">
         <v>-12.055809999999999</v>
@@ -2425,33 +2428,33 @@
         <v>-77.022840000000002</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F44" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G44" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H44">
         <v>-12.056839999999999</v>
@@ -2460,33 +2463,33 @@
         <v>-77.086288999999994</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H45">
         <v>-12.05791188888888</v>
@@ -2495,65 +2498,65 @@
         <v>-77.085793888888887</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F46" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I46">
         <v>-77.081646996680064</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" t="s">
+        <v>154</v>
+      </c>
+      <c r="E47" t="s">
         <v>155</v>
       </c>
-      <c r="B47" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" t="s">
-        <v>151</v>
-      </c>
-      <c r="E47" t="s">
-        <v>152</v>
-      </c>
       <c r="F47" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H47">
         <v>-12.059383211096049</v>
@@ -2562,33 +2565,33 @@
         <v>-77.080684001513475</v>
       </c>
       <c r="J47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G48" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H48">
         <v>-12058578</v>
@@ -2597,33 +2600,33 @@
         <v>-77079825</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F49" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G49" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H49">
         <v>-12058521</v>
@@ -2632,33 +2635,33 @@
         <v>-77079742</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="K49" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E50" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F50" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H50">
         <v>-12058225</v>
@@ -2667,33 +2670,33 @@
         <v>-77079769</v>
       </c>
       <c r="J50" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E51" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F51" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H51">
         <v>-12.054695000000001</v>
@@ -2702,33 +2705,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J51" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E52" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G52" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H52">
         <v>-12.054695000000001</v>
@@ -2737,33 +2740,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J52" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F53" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H53">
         <v>-12.054695000000001</v>
@@ -2772,33 +2775,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J53" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F54" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G54" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H54">
         <v>-12.054695000000001</v>
@@ -2807,33 +2810,33 @@
         <v>-77.084536</v>
       </c>
       <c r="J54" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H55">
         <v>-12.0592408</v>
@@ -2842,33 +2845,33 @@
         <v>-77.083485899999999</v>
       </c>
       <c r="J55" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E56" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G56" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H56">
         <v>-12.058871999999999</v>
@@ -2877,33 +2880,33 @@
         <v>-77.084579500000004</v>
       </c>
       <c r="J56" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F57" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H57">
         <v>-12.058732900000001</v>
@@ -2912,33 +2915,33 @@
         <v>-77.084835699999999</v>
       </c>
       <c r="J57" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F58" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G58" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H58">
         <v>-12.059339</v>
@@ -2947,10 +2950,10 @@
         <v>-77.087202000000005</v>
       </c>
       <c r="J58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -1,21 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70538222-9821-4585-B104-E375EBF398AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -586,13 +577,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11.0"/>
+      <color/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -601,49 +591,40 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -799,7 +780,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="9525" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -808,13 +789,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="38100" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -824,7 +805,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="20000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -833,7 +814,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -842,7 +823,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -852,12 +833,12 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
+            <a:lightRig dir="t" rig="threePt">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
+            <a:bevelT h="25400" w="63500"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -888,7 +869,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -907,7 +888,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -919,23 +900,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="43.43"/>
+    <col customWidth="1" min="2" max="2" width="10.71"/>
+    <col customWidth="1" min="3" max="3" width="12.14"/>
+    <col customWidth="1" min="4" max="4" width="15.71"/>
+    <col customWidth="1" min="5" max="5" width="14.29"/>
+    <col customWidth="1" min="6" max="6" width="13.0"/>
+    <col customWidth="1" min="7" max="7" width="27.43"/>
+    <col customWidth="1" min="8" max="9" width="12.71"/>
+    <col customWidth="1" min="10" max="10" width="13.0"/>
+    <col customWidth="1" min="11" max="11" width="21.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -970,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -996,7 +979,7 @@
         <v>-12.057342</v>
       </c>
       <c r="I2">
-        <v>-77.085965999999999</v>
+        <v>-77.085966</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -1005,7 +988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1027,8 +1010,11 @@
       <c r="G3" t="s">
         <v>22</v>
       </c>
+      <c r="H3">
+        <v>-12.060062</v>
+      </c>
       <c r="I3">
-        <v>-77.081864663826892</v>
+        <v>-77.08186466382689</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -1037,7 +1023,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1063,7 +1049,7 @@
         <v>-12.060062</v>
       </c>
       <c r="I4">
-        <v>-77.083754999999996</v>
+        <v>-77.083755</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -1072,7 +1058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1098,7 +1084,7 @@
         <v>-12.057245</v>
       </c>
       <c r="I5">
-        <v>-77.086871000000002</v>
+        <v>-77.086871</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
@@ -1107,7 +1093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1130,7 +1116,7 @@
         <v>34</v>
       </c>
       <c r="H6">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I6">
         <v>-77.084536</v>
@@ -1142,7 +1128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1168,7 +1154,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I7">
-        <v>-77.085751000000002</v>
+        <v>-77.085751</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -1177,7 +1163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1203,7 +1189,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I8">
-        <v>-77.085751000000002</v>
+        <v>-77.085751</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -1212,7 +1198,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" ht="14.25" customHeight="1">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1238,7 +1224,7 @@
         <v>-12.053938</v>
       </c>
       <c r="I9">
-        <v>-77.086535999999995</v>
+        <v>-77.086536</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -1247,7 +1233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1270,10 +1256,10 @@
         <v>54</v>
       </c>
       <c r="H10">
-        <v>-12.053748000000001</v>
+        <v>-12.053748</v>
       </c>
       <c r="I10">
-        <v>-77.085588000000001</v>
+        <v>-77.085588</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
@@ -1282,7 +1268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -1305,10 +1291,10 @@
         <v>57</v>
       </c>
       <c r="H11">
-        <v>-12.060318000000001</v>
+        <v>-12.060318</v>
       </c>
       <c r="I11">
-        <v>-77.084213000000005</v>
+        <v>-77.084213</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -1317,7 +1303,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1340,10 +1326,10 @@
         <v>61</v>
       </c>
       <c r="H12">
-        <v>-12.060318000000001</v>
+        <v>-12.060318</v>
       </c>
       <c r="I12">
-        <v>-77.084213000000005</v>
+        <v>-77.084213</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1352,7 +1338,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -1378,7 +1364,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I13">
-        <v>-77.086038000000002</v>
+        <v>-77.086038</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -1387,7 +1373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -1413,7 +1399,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I14">
-        <v>-77.086038000000002</v>
+        <v>-77.086038</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -1422,7 +1408,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1448,7 +1434,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I15">
-        <v>-77.086038000000002</v>
+        <v>-77.086038</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1457,7 +1443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1483,7 +1469,7 @@
         <v>-12.059274</v>
       </c>
       <c r="I16">
-        <v>-77.080799999999996</v>
+        <v>-77.0808</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
@@ -1492,7 +1478,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -1514,8 +1500,11 @@
       <c r="G17" t="s">
         <v>75</v>
       </c>
+      <c r="H17">
+        <v>-12.059274</v>
+      </c>
       <c r="I17">
-        <v>-77.081646996680064</v>
+        <v>-77.08164699668006</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -1524,7 +1513,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -1550,7 +1539,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I18">
-        <v>-77.086038000000002</v>
+        <v>-77.086038</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -1559,7 +1548,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1585,7 +1574,7 @@
         <v>-12.059339</v>
       </c>
       <c r="I19">
-        <v>-77.087202000000005</v>
+        <v>-77.087202</v>
       </c>
       <c r="J19" t="s">
         <v>18</v>
@@ -1594,7 +1583,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1617,10 +1606,10 @@
         <v>84</v>
       </c>
       <c r="H20">
-        <v>-12057853</v>
+        <v>-1.2057853E7</v>
       </c>
       <c r="I20">
-        <v>-77079891</v>
+        <v>-7.7079891E7</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
@@ -1629,7 +1618,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -1652,10 +1641,10 @@
         <v>46</v>
       </c>
       <c r="H21">
-        <v>-12057853</v>
+        <v>-1.2057853E7</v>
       </c>
       <c r="I21">
-        <v>-77079891</v>
+        <v>-7.7079891E7</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -1664,7 +1653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -1687,10 +1676,10 @@
         <v>86</v>
       </c>
       <c r="H22">
-        <v>-12057853</v>
+        <v>-1.2057853E7</v>
       </c>
       <c r="I22">
-        <v>-77079891</v>
+        <v>-7.7079891E7</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
@@ -1699,7 +1688,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>83</v>
       </c>
@@ -1722,10 +1711,10 @@
         <v>88</v>
       </c>
       <c r="H23">
-        <v>-12057853</v>
+        <v>-1.2057853E7</v>
       </c>
       <c r="I23">
-        <v>-77079891</v>
+        <v>-7.7079891E7</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -1734,7 +1723,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -1757,10 +1746,10 @@
         <v>90</v>
       </c>
       <c r="H24">
-        <v>-12058354</v>
+        <v>-1.2058354E7</v>
       </c>
       <c r="I24">
-        <v>-77079760</v>
+        <v>-7.707976E7</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -1769,7 +1758,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -1795,7 +1784,7 @@
         <v>-12.054439</v>
       </c>
       <c r="I25">
-        <v>-77.085120000000003</v>
+        <v>-77.08512</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -1804,7 +1793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -1827,10 +1816,10 @@
         <v>54</v>
       </c>
       <c r="H26">
-        <v>-12.054391000000001</v>
+        <v>-12.054391</v>
       </c>
       <c r="I26">
-        <v>-77.084608000000003</v>
+        <v>-77.084608</v>
       </c>
       <c r="J26" t="s">
         <v>30</v>
@@ -1839,7 +1828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -1865,7 +1854,7 @@
         <v>-12.054632</v>
       </c>
       <c r="I27">
-        <v>-77.083718000000005</v>
+        <v>-77.083718</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
@@ -1874,7 +1863,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -1900,7 +1889,7 @@
         <v>-12.054871</v>
       </c>
       <c r="I28">
-        <v>-77.084220999999999</v>
+        <v>-77.084221</v>
       </c>
       <c r="J28" t="s">
         <v>30</v>
@@ -1909,7 +1898,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -1935,7 +1924,7 @@
         <v>-12.054997</v>
       </c>
       <c r="I29">
-        <v>-77.084431300000006</v>
+        <v>-77.0844313</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -1944,7 +1933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -1970,7 +1959,7 @@
         <v>-12.0567391</v>
       </c>
       <c r="I30">
-        <v>-77.085449600000004</v>
+        <v>-77.0854496</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -1979,7 +1968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="A31" t="s">
         <v>92</v>
       </c>
@@ -2002,10 +1991,10 @@
         <v>102</v>
       </c>
       <c r="H31">
-        <v>-12.057642400000001</v>
+        <v>-12.0576424</v>
       </c>
       <c r="I31">
-        <v>-77.085686300000006</v>
+        <v>-77.0856863</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
@@ -2014,7 +2003,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" ht="14.25" customHeight="1">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -2037,10 +2026,10 @@
         <v>109</v>
       </c>
       <c r="H32">
-        <v>-12.056699999999999</v>
+        <v>-12.0567</v>
       </c>
       <c r="I32">
-        <v>-77.084999999999994</v>
+        <v>-77.085</v>
       </c>
       <c r="J32" t="s">
         <v>30</v>
@@ -2049,7 +2038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" ht="14.25" customHeight="1">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -2075,7 +2064,7 @@
         <v>-12.059274</v>
       </c>
       <c r="I33">
-        <v>-77.080799999999996</v>
+        <v>-77.0808</v>
       </c>
       <c r="J33" t="s">
         <v>30</v>
@@ -2084,7 +2073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -2107,7 +2096,7 @@
         <v>113</v>
       </c>
       <c r="H34">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I34">
         <v>-77.084536</v>
@@ -2119,7 +2108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" ht="14.25" customHeight="1">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2142,7 +2131,7 @@
         <v>109</v>
       </c>
       <c r="H35">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I35">
         <v>-77.084536</v>
@@ -2154,7 +2143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" ht="14.25" customHeight="1">
       <c r="A36" t="s">
         <v>114</v>
       </c>
@@ -2177,10 +2166,10 @@
         <v>109</v>
       </c>
       <c r="H36">
-        <v>-12058012</v>
+        <v>-1.2058012E7</v>
       </c>
       <c r="I36">
-        <v>-77079983</v>
+        <v>-7.7079983E7</v>
       </c>
       <c r="J36" t="s">
         <v>30</v>
@@ -2189,7 +2178,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" ht="14.25" customHeight="1">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -2212,10 +2201,10 @@
         <v>120</v>
       </c>
       <c r="H37">
-        <v>-12.059456000000001</v>
+        <v>-12.059456</v>
       </c>
       <c r="I37">
-        <v>-77.090440999999998</v>
+        <v>-77.090441</v>
       </c>
       <c r="J37" t="s">
         <v>18</v>
@@ -2224,7 +2213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2247,10 +2236,10 @@
         <v>125</v>
       </c>
       <c r="H38">
-        <v>-12.059456000000001</v>
+        <v>-12.059456</v>
       </c>
       <c r="I38">
-        <v>-77.090440999999998</v>
+        <v>-77.090441</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
@@ -2259,7 +2248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" ht="14.25" customHeight="1">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -2282,10 +2271,10 @@
         <v>127</v>
       </c>
       <c r="H39">
-        <v>-12.057059000000001</v>
+        <v>-12.057059</v>
       </c>
       <c r="I39">
-        <v>-77.087091000000001</v>
+        <v>-77.087091</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -2294,7 +2283,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" ht="14.25" customHeight="1">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -2317,10 +2306,10 @@
         <v>132</v>
       </c>
       <c r="H40">
-        <v>-12.054278999999999</v>
+        <v>-12.054279</v>
       </c>
       <c r="I40">
-        <v>-77.085412000000005</v>
+        <v>-77.085412</v>
       </c>
       <c r="J40" t="s">
         <v>30</v>
@@ -2329,7 +2318,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" ht="14.25" customHeight="1">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -2355,7 +2344,7 @@
         <v>-12.056659</v>
       </c>
       <c r="I41">
-        <v>-77.086890999999994</v>
+        <v>-77.086891</v>
       </c>
       <c r="J41" t="s">
         <v>30</v>
@@ -2364,7 +2353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" ht="14.25" customHeight="1">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -2390,7 +2379,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I42">
-        <v>-77.085751000000002</v>
+        <v>-77.085751</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2399,7 +2388,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" ht="14.25" customHeight="1">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -2422,10 +2411,10 @@
         <v>143</v>
       </c>
       <c r="H43">
-        <v>-12.055809999999999</v>
+        <v>-12.05581</v>
       </c>
       <c r="I43">
-        <v>-77.022840000000002</v>
+        <v>-77.085751</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -2434,7 +2423,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" ht="14.25" customHeight="1">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2457,10 +2446,10 @@
         <v>147</v>
       </c>
       <c r="H44">
-        <v>-12.056839999999999</v>
+        <v>-12.05684</v>
       </c>
       <c r="I44">
-        <v>-77.086288999999994</v>
+        <v>-77.086289</v>
       </c>
       <c r="J44" t="s">
         <v>30</v>
@@ -2469,7 +2458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" ht="14.25" customHeight="1">
       <c r="A45" t="s">
         <v>148</v>
       </c>
@@ -2495,7 +2484,7 @@
         <v>-12.05791188888888</v>
       </c>
       <c r="I45">
-        <v>-77.085793888888887</v>
+        <v>-77.08579388888889</v>
       </c>
       <c r="J45" t="s">
         <v>30</v>
@@ -2504,7 +2493,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -2526,8 +2515,11 @@
       <c r="G46" t="s">
         <v>157</v>
       </c>
+      <c r="H46">
+        <v>-12.05938321109605</v>
+      </c>
       <c r="I46">
-        <v>-77.081646996680064</v>
+        <v>-77.08164699668006</v>
       </c>
       <c r="J46" t="s">
         <v>18</v>
@@ -2536,7 +2528,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" ht="14.25" customHeight="1">
       <c r="A47" t="s">
         <v>158</v>
       </c>
@@ -2559,10 +2551,10 @@
         <v>160</v>
       </c>
       <c r="H47">
-        <v>-12.059383211096049</v>
+        <v>-12.05938321109605</v>
       </c>
       <c r="I47">
-        <v>-77.080684001513475</v>
+        <v>-77.08068400151348</v>
       </c>
       <c r="J47" t="s">
         <v>18</v>
@@ -2571,7 +2563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" ht="14.25" customHeight="1">
       <c r="A48" t="s">
         <v>114</v>
       </c>
@@ -2594,10 +2586,10 @@
         <v>161</v>
       </c>
       <c r="H48">
-        <v>-12058578</v>
+        <v>-1.2058578E7</v>
       </c>
       <c r="I48">
-        <v>-77079825</v>
+        <v>-7.7079825E7</v>
       </c>
       <c r="J48" t="s">
         <v>30</v>
@@ -2606,7 +2598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" ht="14.25" customHeight="1">
       <c r="A49" t="s">
         <v>114</v>
       </c>
@@ -2629,10 +2621,10 @@
         <v>162</v>
       </c>
       <c r="H49">
-        <v>-12058521</v>
+        <v>-1.2058521E7</v>
       </c>
       <c r="I49">
-        <v>-77079742</v>
+        <v>-7.7079742E7</v>
       </c>
       <c r="J49" t="s">
         <v>159</v>
@@ -2641,7 +2633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" ht="14.25" customHeight="1">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -2664,10 +2656,10 @@
         <v>147</v>
       </c>
       <c r="H50">
-        <v>-12058225</v>
+        <v>-1.2058225E7</v>
       </c>
       <c r="I50">
-        <v>-77079769</v>
+        <v>-7.7079769E7</v>
       </c>
       <c r="J50" t="s">
         <v>30</v>
@@ -2676,7 +2668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" ht="14.25" customHeight="1">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -2699,7 +2691,7 @@
         <v>135</v>
       </c>
       <c r="H51">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I51">
         <v>-77.084536</v>
@@ -2711,7 +2703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" ht="14.25" customHeight="1">
       <c r="A52" t="s">
         <v>31</v>
       </c>
@@ -2734,7 +2726,7 @@
         <v>164</v>
       </c>
       <c r="H52">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I52">
         <v>-77.084536</v>
@@ -2746,7 +2738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" ht="14.25" customHeight="1">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -2769,7 +2761,7 @@
         <v>167</v>
       </c>
       <c r="H53">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I53">
         <v>-77.084536</v>
@@ -2781,7 +2773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" ht="14.25" customHeight="1">
       <c r="A54" t="s">
         <v>31</v>
       </c>
@@ -2804,7 +2796,7 @@
         <v>147</v>
       </c>
       <c r="H54">
-        <v>-12.054695000000001</v>
+        <v>-12.054695</v>
       </c>
       <c r="I54">
         <v>-77.084536</v>
@@ -2816,7 +2808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" ht="14.25" customHeight="1">
       <c r="A55" t="s">
         <v>92</v>
       </c>
@@ -2842,7 +2834,7 @@
         <v>-12.0592408</v>
       </c>
       <c r="I55">
-        <v>-77.083485899999999</v>
+        <v>-77.0834859</v>
       </c>
       <c r="J55" t="s">
         <v>30</v>
@@ -2851,7 +2843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" ht="14.25" customHeight="1">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -2874,10 +2866,10 @@
         <v>174</v>
       </c>
       <c r="H56">
-        <v>-12.058871999999999</v>
+        <v>-12.058872</v>
       </c>
       <c r="I56">
-        <v>-77.084579500000004</v>
+        <v>-77.0845795</v>
       </c>
       <c r="J56" t="s">
         <v>30</v>
@@ -2886,7 +2878,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" ht="14.25" customHeight="1">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2909,10 +2901,10 @@
         <v>179</v>
       </c>
       <c r="H57">
-        <v>-12.058732900000001</v>
+        <v>-12.0587329</v>
       </c>
       <c r="I57">
-        <v>-77.084835699999999</v>
+        <v>-77.0848357</v>
       </c>
       <c r="J57" t="s">
         <v>30</v>
@@ -2921,7 +2913,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" ht="14.25" customHeight="1">
       <c r="A58" t="s">
         <v>180</v>
       </c>
@@ -2947,7 +2939,7 @@
         <v>-12.059339</v>
       </c>
       <c r="I58">
-        <v>-77.087202000000005</v>
+        <v>-77.087202</v>
       </c>
       <c r="J58" t="s">
         <v>18</v>
@@ -2956,7 +2948,52 @@
         <v>186</v>
       </c>
     </row>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -578,13 +578,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.0"/>
-      <color/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -600,9 +601,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2410,8 +2414,8 @@
       <c r="G43" t="s">
         <v>143</v>
       </c>
-      <c r="H43">
-        <v>-12.05581</v>
+      <c r="H43" s="1">
+        <v>-12.05684</v>
       </c>
       <c r="I43">
         <v>-77.085751</v>

--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7880D6-7E3D-45AD-A848-BCA4437703A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -577,58 +586,68 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -784,7 +803,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln cap="flat" cmpd="sng" w="9525" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -793,13 +812,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="38100" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -809,7 +828,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="20000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -818,7 +837,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -827,7 +846,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -837,12 +856,12 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT h="25400" w="63500"/>
+            <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -873,7 +892,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -892,7 +911,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -904,25 +923,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K100"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="43.43"/>
-    <col customWidth="1" min="2" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="12.14"/>
-    <col customWidth="1" min="4" max="4" width="15.71"/>
-    <col customWidth="1" min="5" max="5" width="14.29"/>
-    <col customWidth="1" min="6" max="6" width="13.0"/>
-    <col customWidth="1" min="7" max="7" width="27.43"/>
-    <col customWidth="1" min="8" max="9" width="12.71"/>
-    <col customWidth="1" min="10" max="10" width="13.0"/>
-    <col customWidth="1" min="11" max="11" width="21.71"/>
+    <col min="1" max="1" width="43.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:11" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -983,7 +1000,7 @@
         <v>-12.057342</v>
       </c>
       <c r="I2">
-        <v>-77.085966</v>
+        <v>-77.085965999999999</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -992,7 +1009,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1035,7 @@
         <v>-12.060062</v>
       </c>
       <c r="I3">
-        <v>-77.08186466382689</v>
+        <v>-77.081864663826892</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -1027,7 +1044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1053,7 +1070,7 @@
         <v>-12.060062</v>
       </c>
       <c r="I4">
-        <v>-77.083755</v>
+        <v>-77.083754999999996</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -1062,7 +1079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1088,7 +1105,7 @@
         <v>-12.057245</v>
       </c>
       <c r="I5">
-        <v>-77.086871</v>
+        <v>-77.086871000000002</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
@@ -1097,7 +1114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1120,7 +1137,7 @@
         <v>34</v>
       </c>
       <c r="H6">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I6">
         <v>-77.084536</v>
@@ -1132,7 +1149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1158,7 +1175,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I7">
-        <v>-77.085751</v>
+        <v>-77.085751000000002</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -1167,7 +1184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1193,7 +1210,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I8">
-        <v>-77.085751</v>
+        <v>-77.085751000000002</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -1202,7 +1219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1228,7 +1245,7 @@
         <v>-12.053938</v>
       </c>
       <c r="I9">
-        <v>-77.086536</v>
+        <v>-77.086535999999995</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -1237,7 +1254,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:11" ht="14.25" customHeight="1">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1260,10 +1277,10 @@
         <v>54</v>
       </c>
       <c r="H10">
-        <v>-12.053748</v>
+        <v>-12.053748000000001</v>
       </c>
       <c r="I10">
-        <v>-77.085588</v>
+        <v>-77.085588000000001</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
@@ -1272,7 +1289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:11" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -1295,10 +1312,10 @@
         <v>57</v>
       </c>
       <c r="H11">
-        <v>-12.060318</v>
+        <v>-12.060318000000001</v>
       </c>
       <c r="I11">
-        <v>-77.084213</v>
+        <v>-77.084213000000005</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -1307,7 +1324,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1330,10 +1347,10 @@
         <v>61</v>
       </c>
       <c r="H12">
-        <v>-12.060318</v>
+        <v>-12.060318000000001</v>
       </c>
       <c r="I12">
-        <v>-77.084213</v>
+        <v>-77.084213000000005</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1342,7 +1359,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -1368,7 +1385,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I13">
-        <v>-77.086038</v>
+        <v>-77.086038000000002</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -1377,7 +1394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -1403,7 +1420,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I14">
-        <v>-77.086038</v>
+        <v>-77.086038000000002</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -1412,7 +1429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1438,7 +1455,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I15">
-        <v>-77.086038</v>
+        <v>-77.086038000000002</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1447,7 +1464,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:11" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1473,7 +1490,7 @@
         <v>-12.059274</v>
       </c>
       <c r="I16">
-        <v>-77.0808</v>
+        <v>-77.080799999999996</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
@@ -1482,7 +1499,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -1508,7 +1525,7 @@
         <v>-12.059274</v>
       </c>
       <c r="I17">
-        <v>-77.08164699668006</v>
+        <v>-77.081646996680064</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -1517,7 +1534,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -1543,7 +1560,7 @@
         <v>-12.057501</v>
       </c>
       <c r="I18">
-        <v>-77.086038</v>
+        <v>-77.086038000000002</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -1552,7 +1569,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1578,7 +1595,7 @@
         <v>-12.059339</v>
       </c>
       <c r="I19">
-        <v>-77.087202</v>
+        <v>-77.087202000000005</v>
       </c>
       <c r="J19" t="s">
         <v>18</v>
@@ -1587,7 +1604,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:11" ht="14.25" customHeight="1">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1610,10 +1627,10 @@
         <v>84</v>
       </c>
       <c r="H20">
-        <v>-1.2057853E7</v>
+        <v>-12057853</v>
       </c>
       <c r="I20">
-        <v>-7.7079891E7</v>
+        <v>-77079891</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
@@ -1622,7 +1639,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -1645,10 +1662,10 @@
         <v>46</v>
       </c>
       <c r="H21">
-        <v>-1.2057853E7</v>
+        <v>-12057853</v>
       </c>
       <c r="I21">
-        <v>-7.7079891E7</v>
+        <v>-77079891</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -1657,7 +1674,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:11" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -1680,10 +1697,10 @@
         <v>86</v>
       </c>
       <c r="H22">
-        <v>-1.2057853E7</v>
+        <v>-12057853</v>
       </c>
       <c r="I22">
-        <v>-7.7079891E7</v>
+        <v>-77079891</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
@@ -1692,7 +1709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:11" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>83</v>
       </c>
@@ -1715,10 +1732,10 @@
         <v>88</v>
       </c>
       <c r="H23">
-        <v>-1.2057853E7</v>
+        <v>-12057853</v>
       </c>
       <c r="I23">
-        <v>-7.7079891E7</v>
+        <v>-77079891</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -1727,7 +1744,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:11" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -1750,10 +1767,10 @@
         <v>90</v>
       </c>
       <c r="H24">
-        <v>-1.2058354E7</v>
+        <v>-12058354</v>
       </c>
       <c r="I24">
-        <v>-7.707976E7</v>
+        <v>-77079760</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -1762,7 +1779,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:11" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -1788,7 +1805,7 @@
         <v>-12.054439</v>
       </c>
       <c r="I25">
-        <v>-77.08512</v>
+        <v>-77.085120000000003</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -1797,7 +1814,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:11" ht="14.25" customHeight="1">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -1820,10 +1837,10 @@
         <v>54</v>
       </c>
       <c r="H26">
-        <v>-12.054391</v>
+        <v>-12.054391000000001</v>
       </c>
       <c r="I26">
-        <v>-77.084608</v>
+        <v>-77.084608000000003</v>
       </c>
       <c r="J26" t="s">
         <v>30</v>
@@ -1832,7 +1849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:11" ht="14.25" customHeight="1">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -1858,7 +1875,7 @@
         <v>-12.054632</v>
       </c>
       <c r="I27">
-        <v>-77.083718</v>
+        <v>-77.083718000000005</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
@@ -1867,7 +1884,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -1893,7 +1910,7 @@
         <v>-12.054871</v>
       </c>
       <c r="I28">
-        <v>-77.084221</v>
+        <v>-77.084220999999999</v>
       </c>
       <c r="J28" t="s">
         <v>30</v>
@@ -1902,7 +1919,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:11" ht="14.25" customHeight="1">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -1928,7 +1945,7 @@
         <v>-12.054997</v>
       </c>
       <c r="I29">
-        <v>-77.0844313</v>
+        <v>-77.084431300000006</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -1937,7 +1954,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -1963,7 +1980,7 @@
         <v>-12.0567391</v>
       </c>
       <c r="I30">
-        <v>-77.0854496</v>
+        <v>-77.085449600000004</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -1972,7 +1989,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1">
       <c r="A31" t="s">
         <v>92</v>
       </c>
@@ -1995,10 +2012,10 @@
         <v>102</v>
       </c>
       <c r="H31">
-        <v>-12.0576424</v>
+        <v>-12.057642400000001</v>
       </c>
       <c r="I31">
-        <v>-77.0856863</v>
+        <v>-77.085686300000006</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
@@ -2007,7 +2024,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:11" ht="14.25" customHeight="1">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -2030,10 +2047,10 @@
         <v>109</v>
       </c>
       <c r="H32">
-        <v>-12.0567</v>
+        <v>-12.056699999999999</v>
       </c>
       <c r="I32">
-        <v>-77.085</v>
+        <v>-77.084999999999994</v>
       </c>
       <c r="J32" t="s">
         <v>30</v>
@@ -2042,7 +2059,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -2068,7 +2085,7 @@
         <v>-12.059274</v>
       </c>
       <c r="I33">
-        <v>-77.0808</v>
+        <v>-77.080799999999996</v>
       </c>
       <c r="J33" t="s">
         <v>30</v>
@@ -2077,7 +2094,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:11" ht="14.25" customHeight="1">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -2100,7 +2117,7 @@
         <v>113</v>
       </c>
       <c r="H34">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I34">
         <v>-77.084536</v>
@@ -2112,7 +2129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:11" ht="14.25" customHeight="1">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2135,7 +2152,7 @@
         <v>109</v>
       </c>
       <c r="H35">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I35">
         <v>-77.084536</v>
@@ -2147,7 +2164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:11" ht="14.25" customHeight="1">
       <c r="A36" t="s">
         <v>114</v>
       </c>
@@ -2170,10 +2187,10 @@
         <v>109</v>
       </c>
       <c r="H36">
-        <v>-1.2058012E7</v>
+        <v>-12058012</v>
       </c>
       <c r="I36">
-        <v>-7.7079983E7</v>
+        <v>-77079983</v>
       </c>
       <c r="J36" t="s">
         <v>30</v>
@@ -2182,7 +2199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:11" ht="14.25" customHeight="1">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -2205,10 +2222,10 @@
         <v>120</v>
       </c>
       <c r="H37">
-        <v>-12.059456</v>
+        <v>-12.057256000000001</v>
       </c>
       <c r="I37">
-        <v>-77.090441</v>
+        <v>-77.083440999999993</v>
       </c>
       <c r="J37" t="s">
         <v>18</v>
@@ -2217,7 +2234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:11" ht="14.25" customHeight="1">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2240,10 +2257,10 @@
         <v>125</v>
       </c>
       <c r="H38">
-        <v>-12.059456</v>
+        <v>-12.059456000000001</v>
       </c>
       <c r="I38">
-        <v>-77.090441</v>
+        <v>-77.085441000000003</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
@@ -2252,7 +2269,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:11" ht="14.25" customHeight="1">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -2275,10 +2292,10 @@
         <v>127</v>
       </c>
       <c r="H39">
-        <v>-12.057059</v>
+        <v>-12.057059000000001</v>
       </c>
       <c r="I39">
-        <v>-77.087091</v>
+        <v>-77.087091000000001</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -2287,7 +2304,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:11" ht="14.25" customHeight="1">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -2310,10 +2327,10 @@
         <v>132</v>
       </c>
       <c r="H40">
-        <v>-12.054279</v>
+        <v>-12.054278999999999</v>
       </c>
       <c r="I40">
-        <v>-77.085412</v>
+        <v>-77.085412000000005</v>
       </c>
       <c r="J40" t="s">
         <v>30</v>
@@ -2322,7 +2339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:11" ht="14.25" customHeight="1">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -2348,7 +2365,7 @@
         <v>-12.056659</v>
       </c>
       <c r="I41">
-        <v>-77.086891</v>
+        <v>-77.086890999999994</v>
       </c>
       <c r="J41" t="s">
         <v>30</v>
@@ -2357,7 +2374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:11" ht="14.25" customHeight="1">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -2383,7 +2400,7 @@
         <v>-12.053594</v>
       </c>
       <c r="I42">
-        <v>-77.085751</v>
+        <v>-77.085751000000002</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2392,7 +2409,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:11" ht="14.25" customHeight="1">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -2415,10 +2432,10 @@
         <v>143</v>
       </c>
       <c r="H43" s="1">
-        <v>-12.05684</v>
+        <v>-12.056839999999999</v>
       </c>
       <c r="I43">
-        <v>-77.085751</v>
+        <v>-77.085751000000002</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -2427,7 +2444,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:11" ht="14.25" customHeight="1">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2450,10 +2467,10 @@
         <v>147</v>
       </c>
       <c r="H44">
-        <v>-12.05684</v>
+        <v>-12.056839999999999</v>
       </c>
       <c r="I44">
-        <v>-77.086289</v>
+        <v>-77.086288999999994</v>
       </c>
       <c r="J44" t="s">
         <v>30</v>
@@ -2462,7 +2479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:11" ht="14.25" customHeight="1">
       <c r="A45" t="s">
         <v>148</v>
       </c>
@@ -2488,7 +2505,7 @@
         <v>-12.05791188888888</v>
       </c>
       <c r="I45">
-        <v>-77.08579388888889</v>
+        <v>-77.085793888888887</v>
       </c>
       <c r="J45" t="s">
         <v>30</v>
@@ -2497,7 +2514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:11" ht="14.25" customHeight="1">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -2520,10 +2537,10 @@
         <v>157</v>
       </c>
       <c r="H46">
-        <v>-12.05938321109605</v>
+        <v>-12.059383211096049</v>
       </c>
       <c r="I46">
-        <v>-77.08164699668006</v>
+        <v>-77.081646996680064</v>
       </c>
       <c r="J46" t="s">
         <v>18</v>
@@ -2532,7 +2549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:11" ht="14.25" customHeight="1">
       <c r="A47" t="s">
         <v>158</v>
       </c>
@@ -2555,10 +2572,10 @@
         <v>160</v>
       </c>
       <c r="H47">
-        <v>-12.05938321109605</v>
+        <v>-12.059383211096049</v>
       </c>
       <c r="I47">
-        <v>-77.08068400151348</v>
+        <v>-77.080684001513475</v>
       </c>
       <c r="J47" t="s">
         <v>18</v>
@@ -2567,7 +2584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:11" ht="14.25" customHeight="1">
       <c r="A48" t="s">
         <v>114</v>
       </c>
@@ -2590,10 +2607,10 @@
         <v>161</v>
       </c>
       <c r="H48">
-        <v>-1.2058578E7</v>
+        <v>-12058578</v>
       </c>
       <c r="I48">
-        <v>-7.7079825E7</v>
+        <v>-77079825</v>
       </c>
       <c r="J48" t="s">
         <v>30</v>
@@ -2602,7 +2619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:11" ht="14.25" customHeight="1">
       <c r="A49" t="s">
         <v>114</v>
       </c>
@@ -2625,10 +2642,10 @@
         <v>162</v>
       </c>
       <c r="H49">
-        <v>-1.2058521E7</v>
+        <v>-12058521</v>
       </c>
       <c r="I49">
-        <v>-7.7079742E7</v>
+        <v>-77079742</v>
       </c>
       <c r="J49" t="s">
         <v>159</v>
@@ -2637,7 +2654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:11" ht="14.25" customHeight="1">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -2660,10 +2677,10 @@
         <v>147</v>
       </c>
       <c r="H50">
-        <v>-1.2058225E7</v>
+        <v>-12058225</v>
       </c>
       <c r="I50">
-        <v>-7.7079769E7</v>
+        <v>-77079769</v>
       </c>
       <c r="J50" t="s">
         <v>30</v>
@@ -2672,7 +2689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:11" ht="14.25" customHeight="1">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -2695,7 +2712,7 @@
         <v>135</v>
       </c>
       <c r="H51">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I51">
         <v>-77.084536</v>
@@ -2707,7 +2724,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:11" ht="14.25" customHeight="1">
       <c r="A52" t="s">
         <v>31</v>
       </c>
@@ -2730,7 +2747,7 @@
         <v>164</v>
       </c>
       <c r="H52">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I52">
         <v>-77.084536</v>
@@ -2742,7 +2759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:11" ht="14.25" customHeight="1">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -2765,7 +2782,7 @@
         <v>167</v>
       </c>
       <c r="H53">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I53">
         <v>-77.084536</v>
@@ -2777,7 +2794,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:11" ht="14.25" customHeight="1">
       <c r="A54" t="s">
         <v>31</v>
       </c>
@@ -2800,7 +2817,7 @@
         <v>147</v>
       </c>
       <c r="H54">
-        <v>-12.054695</v>
+        <v>-12.054695000000001</v>
       </c>
       <c r="I54">
         <v>-77.084536</v>
@@ -2812,7 +2829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:11" ht="14.25" customHeight="1">
       <c r="A55" t="s">
         <v>92</v>
       </c>
@@ -2838,7 +2855,7 @@
         <v>-12.0592408</v>
       </c>
       <c r="I55">
-        <v>-77.0834859</v>
+        <v>-77.083485899999999</v>
       </c>
       <c r="J55" t="s">
         <v>30</v>
@@ -2847,7 +2864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:11" ht="14.25" customHeight="1">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -2870,10 +2887,10 @@
         <v>174</v>
       </c>
       <c r="H56">
-        <v>-12.058872</v>
+        <v>-12.058871999999999</v>
       </c>
       <c r="I56">
-        <v>-77.0845795</v>
+        <v>-77.084579500000004</v>
       </c>
       <c r="J56" t="s">
         <v>30</v>
@@ -2882,7 +2899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:11" ht="14.25" customHeight="1">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2905,10 +2922,10 @@
         <v>179</v>
       </c>
       <c r="H57">
-        <v>-12.0587329</v>
+        <v>-12.058732900000001</v>
       </c>
       <c r="I57">
-        <v>-77.0848357</v>
+        <v>-77.084835699999999</v>
       </c>
       <c r="J57" t="s">
         <v>30</v>
@@ -2917,7 +2934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="1:11" ht="14.25" customHeight="1">
       <c r="A58" t="s">
         <v>180</v>
       </c>
@@ -2943,7 +2960,7 @@
         <v>-12.059339</v>
       </c>
       <c r="I58">
-        <v>-77.087202</v>
+        <v>-77.087202000000005</v>
       </c>
       <c r="J58" t="s">
         <v>18</v>
@@ -2952,12 +2969,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:11" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:11" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:11" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:11" ht="14.25" customHeight="1"/>
+    <row r="63" spans="1:11" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:11" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -2995,9 +3012,7 @@
     <row r="99" ht="14.25" customHeight="1"/>
     <row r="100" ht="14.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/fauna.xlsx
+++ b/fauna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\bioConservaPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7880D6-7E3D-45AD-A848-BCA4437703A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549C66FC-D7CE-4674-8452-61DCE6A45FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2257,10 +2257,10 @@
         <v>125</v>
       </c>
       <c r="H38">
-        <v>-12.059456000000001</v>
+        <v>-12.057456</v>
       </c>
       <c r="I38">
-        <v>-77.085441000000003</v>
+        <v>-77.082441000000003</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
